--- a/docs/Manual_Test_Cases.xlsx
+++ b/docs/Manual_Test_Cases.xlsx
@@ -1430,7 +1430,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1447,85 +1447,54 @@
     <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
+    <row r="1" spans="1:12">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>E2E Playwright Automation Framework - Danh sach test case manual</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1534,22 +1503,22 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
@@ -1558,36 +1527,36 @@
         <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
@@ -1596,12 +1565,12 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1613,19 +1582,19 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
@@ -1639,31 +1608,31 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J6" t="s">
         <v>21</v>
@@ -1672,12 +1641,12 @@
         <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1689,19 +1658,19 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J7" t="s">
         <v>21</v>
@@ -1715,31 +1684,31 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J8" t="s">
         <v>21</v>
@@ -1753,7 +1722,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1765,25 +1734,25 @@
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
         <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
@@ -1791,45 +1760,45 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
@@ -1841,33 +1810,33 @@
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J11" t="s">
         <v>21</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
@@ -1879,16 +1848,16 @@
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s">
         <v>80</v>
@@ -1897,15 +1866,15 @@
         <v>21</v>
       </c>
       <c r="K12" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
@@ -1917,16 +1886,16 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
         <v>80</v>
@@ -1943,37 +1912,37 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
         <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="L14" t="s">
         <v>30</v>
@@ -1981,7 +1950,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
         <v>69</v>
@@ -1993,19 +1962,19 @@
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I15" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -2019,45 +1988,45 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F16" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H16" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="I16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K16" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L16" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
         <v>105</v>
@@ -2069,19 +2038,19 @@
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H17" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="J17" t="s">
         <v>21</v>
@@ -2090,42 +2059,42 @@
         <v>22</v>
       </c>
       <c r="L17" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s">
         <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H18" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="L18" t="s">
         <v>30</v>
@@ -2133,7 +2102,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
         <v>105</v>
@@ -2145,19 +2114,19 @@
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F19" t="s">
         <v>107</v>
       </c>
       <c r="G19" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H19" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -2171,7 +2140,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s">
         <v>105</v>
@@ -2183,19 +2152,19 @@
         <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F20" t="s">
         <v>107</v>
       </c>
       <c r="G20" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J20" t="s">
         <v>38</v>
@@ -2209,7 +2178,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
         <v>105</v>
@@ -2221,19 +2190,19 @@
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F21" t="s">
         <v>107</v>
       </c>
       <c r="G21" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I21" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
@@ -2247,45 +2216,45 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F22" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G22" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I22" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="J22" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K22" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L22" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s">
         <v>138</v>
@@ -2297,16 +2266,16 @@
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F23" t="s">
         <v>140</v>
       </c>
       <c r="G23" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H23" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I23" t="s">
         <v>143</v>
@@ -2323,7 +2292,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
         <v>138</v>
@@ -2335,16 +2304,16 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F24" t="s">
         <v>140</v>
       </c>
       <c r="G24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I24" t="s">
         <v>143</v>
@@ -2356,33 +2325,33 @@
         <v>22</v>
       </c>
       <c r="L24" t="s">
-        <v>30</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s">
         <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I25" t="s">
         <v>143</v>
@@ -2399,37 +2368,37 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F26" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G26" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="H26" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I26" t="s">
         <v>143</v>
       </c>
       <c r="J26" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="L26" t="s">
         <v>30</v>
@@ -2437,28 +2406,28 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s">
         <v>159</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
         <v>160</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F27" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G27" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H27" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="I27" t="s">
         <v>143</v>
@@ -2475,7 +2444,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
         <v>159</v>
@@ -2487,19 +2456,19 @@
         <v>160</v>
       </c>
       <c r="E28" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G28" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H28" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I28" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="J28" t="s">
         <v>165</v>
@@ -2513,7 +2482,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B29" t="s">
         <v>159</v>
@@ -2525,19 +2494,19 @@
         <v>160</v>
       </c>
       <c r="E29" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F29" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G29" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I29" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J29" t="s">
         <v>165</v>
@@ -2549,8 +2518,232 @@
         <v>30</v>
       </c>
     </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" t="s">
+        <v>179</v>
+      </c>
+      <c r="F30" t="s">
+        <v>180</v>
+      </c>
+      <c r="G30" t="s">
+        <v>181</v>
+      </c>
+      <c r="H30" t="s">
+        <v>182</v>
+      </c>
+      <c r="I30" t="s">
+        <v>183</v>
+      </c>
+      <c r="J30" t="s">
+        <v>165</v>
+      </c>
+      <c r="K30" t="s">
+        <v>166</v>
+      </c>
+      <c r="L30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FRAME-001</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Frames</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kiem tra noi dung trong ca hai frame</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nguoi dung dang o trang Frames</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1. Mo trang Frames`n2. Doc sample heading trong frame1 va frame2</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ca hai frame hien thi This is a sample page</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Smoke case</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FRAME-002</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Frames</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kiem tra kich thuoc frame lon va frame nho</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nguoi dung dang o trang Frames</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1. Mo trang Frames`n2. So sanh bounding box cua frame1 va frame2</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Chieu rong va chieu cao cua frame thu nhat lon hon frame thu hai</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FRAME-003</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nested Frames</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kiem tra noi dung trong nested frames</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nguoi dung dang o trang Nested Frames</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1. Mo trang Nested Frames`n2. Doc noi dung parent frame`n3. Doc noi dung child iframe</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Parent frame hien thi Parent frame va child iframe hien thi Child Iframe</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Dung nested frameLocator</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A2:L33"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Manual_Test_Cases.xlsx
+++ b/docs/Manual_Test_Cases.xlsx
@@ -1,42 +1,20 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>1</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="1" baseType="lpstr">
-      <vt:lpstr>Manual Test Cases</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>14.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="630" yWindow="540" windowWidth="27495" windowHeight="11955"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Manual Test Cases" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:title>Manual Test Cases</dc:title>
-  <dc:creator>Codex</dc:creator>
-  <cp:lastModifiedBy>Windows User</cp:lastModifiedBy>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-06-09T03:22:43Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="184">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="353">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -588,11 +566,518 @@
   </si>
   <si>
     <t>BASE_URL=https://demoqa.com</t>
+  </si>
+  <si>
+    <t>E2E Playwright Automation Framework - Danh sach test case manual</t>
+  </si>
+  <si>
+    <t>FRAME-001</t>
+  </si>
+  <si>
+    <t>Frames</t>
+  </si>
+  <si>
+    <t>Kiem tra noi dung trong ca hai frame</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Frames</t>
+  </si>
+  <si>
+    <t>1. Mo trang Frames`n2. Doc sample heading trong frame1 va frame2</t>
+  </si>
+  <si>
+    <t>Ca hai frame hien thi This is a sample page</t>
+  </si>
+  <si>
+    <t>FRAME-002</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Kiem tra kich thuoc frame lon va frame nho</t>
+  </si>
+  <si>
+    <t>1. Mo trang Frames`n2. So sanh bounding box cua frame1 va frame2</t>
+  </si>
+  <si>
+    <t>Chieu rong va chieu cao cua frame thu nhat lon hon frame thu hai</t>
+  </si>
+  <si>
+    <t>FRAME-003</t>
+  </si>
+  <si>
+    <t>Nested Frames</t>
+  </si>
+  <si>
+    <t>Kiem tra noi dung trong nested frames</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Nested Frames</t>
+  </si>
+  <si>
+    <t>1. Mo trang Nested Frames`n2. Doc noi dung parent frame`n3. Doc noi dung child iframe</t>
+  </si>
+  <si>
+    <t>Parent frame hien thi Parent frame va child iframe hien thi Child Iframe</t>
+  </si>
+  <si>
+    <t>Dung nested frameLocator</t>
+  </si>
+  <si>
+    <t>Boundary</t>
+  </si>
+  <si>
+    <t>Dang nhap that bai voi password 100 ky tu</t>
+  </si>
+  <si>
+    <t>Da co user hop le tren Book Store</t>
+  </si>
+  <si>
+    <t>1. Mo trang Login`n2. Nhap username hop le`n3. Nhap password gom 100 ky tu`n4. Click Login</t>
+  </si>
+  <si>
+    <t>He thong hien thi loi dang nhap va van o trang Login</t>
+  </si>
+  <si>
+    <t>Password = 100 ky tu A</t>
+  </si>
+  <si>
+    <t>Boundary password length</t>
+  </si>
+  <si>
+    <t>AUTH-009</t>
+  </si>
+  <si>
+    <t>Edge Case</t>
+  </si>
+  <si>
+    <t>Dang nhap that bai khi username co khoang trang dau/cuoi</t>
+  </si>
+  <si>
+    <t>1. Mo trang Login`n2. Nhap username hop le kem space dau/cuoi`n3. Nhap password hop le`n4. Click Login</t>
+  </si>
+  <si>
+    <t>He thong khong trim sai logic, hien thi loi va van o trang Login</t>
+  </si>
+  <si>
+    <t>Username = "  valid_user  "</t>
+  </si>
+  <si>
+    <t>Whitespace input</t>
+  </si>
+  <si>
+    <t>AUTH-010</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Dang nhap that bai voi chuoi injection-like</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Login</t>
+  </si>
+  <si>
+    <t>1. Nhap username dang SQL injection`n2. Nhap password dang SQL injection`n3. Click Login</t>
+  </si>
+  <si>
+    <t>He thong tu choi dang nhap, khong bi bypass</t>
+  </si>
+  <si>
+    <t>' OR '1'='1</t>
+  </si>
+  <si>
+    <t>Security negative</t>
+  </si>
+  <si>
+    <t>TXT-002</t>
+  </si>
+  <si>
+    <t>Text Box</t>
+  </si>
+  <si>
+    <t>Submit Text Box voi du lieu dai va ky tu dac biet</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Text Box</t>
+  </si>
+  <si>
+    <t>1. Nhap full name co dau gach/noi`n2. Nhap email hop le`n3. Nhap address dai 100+ ky tu`n4. Submit form</t>
+  </si>
+  <si>
+    <t>Output hien thi dung toan bo du lieu da submit</t>
+  </si>
+  <si>
+    <t>Ten co dau nhay, address dai, symbols</t>
+  </si>
+  <si>
+    <t>Manual mindset input variety</t>
+  </si>
+  <si>
+    <t>TXT-003</t>
+  </si>
+  <si>
+    <t>Text Box tu choi email sai format</t>
+  </si>
+  <si>
+    <t>1. Nhap cac field hop le`n2. Nhap email sai format`n3. Click Submit</t>
+  </si>
+  <si>
+    <t>Output khong hien thi va email field co validation error</t>
+  </si>
+  <si>
+    <t>qa+invalid..dots@example..com</t>
+  </si>
+  <si>
+    <t>Email validation</t>
+  </si>
+  <si>
+    <t>ALERT-002</t>
+  </si>
+  <si>
+    <t>Alerts</t>
+  </si>
+  <si>
+    <t>Dismiss confirm alert</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Alerts</t>
+  </si>
+  <si>
+    <t>1. Click Confirm alert`n2. Chon Cancel/Dismiss tren alert</t>
+  </si>
+  <si>
+    <t>Ket qua hien thi You selected Cancel</t>
+  </si>
+  <si>
+    <t>Alternate confirm path</t>
+  </si>
+  <si>
+    <t>ALERT-003</t>
+  </si>
+  <si>
+    <t>Nhap prompt alert voi chuoi dai va ky tu dac biet</t>
+  </si>
+  <si>
+    <t>1. Click Prompt alert`n2. Nhap chuoi dai kem ky tu dac biet`n3. Accept alert</t>
+  </si>
+  <si>
+    <t>Prompt result hien thi dung chuoi da nhap</t>
+  </si>
+  <si>
+    <t>Manual QA 123 !@#$%^&amp;*() + 80 ky tu X</t>
+  </si>
+  <si>
+    <t>Prompt boundary</t>
+  </si>
+  <si>
+    <t>MODAL-003</t>
+  </si>
+  <si>
+    <t>Modal Dialogs</t>
+  </si>
+  <si>
+    <t>Dong small modal bang nut X</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Modal Dialogs</t>
+  </si>
+  <si>
+    <t>1. Mo Small modal`n2. Click nut X tren header modal</t>
+  </si>
+  <si>
+    <t>Modal dong lai va trang Modal Dialogs van hien thi</t>
+  </si>
+  <si>
+    <t>Alternate close action</t>
+  </si>
+  <si>
+    <t>MODAL-004</t>
+  </si>
+  <si>
+    <t>Dong large modal bang phim Escape</t>
+  </si>
+  <si>
+    <t>1. Mo Large modal`n2. Bam phim Escape</t>
+  </si>
+  <si>
+    <t>Keyboard interaction</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Submit Practice Form voi gender Female va ten dai</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Practice Form</t>
+  </si>
+  <si>
+    <t>1. Nhap first name/last name co dau gach/noi`n2. Chon Female`n3. Nhap mobile hop le`n4. Submit</t>
+  </si>
+  <si>
+    <t>Modal hien thi dung thong tin edge-case</t>
+  </si>
+  <si>
+    <t>Anne-Marie O'Connor Smith</t>
+  </si>
+  <si>
+    <t>Data diversity</t>
+  </si>
+  <si>
+    <t>Practice Form bao loi khi bo trong required fields</t>
+  </si>
+  <si>
+    <t>1. Khong nhap du lieu bat buoc`n2. Click Submit</t>
+  </si>
+  <si>
+    <t>Modal khong mo va cac field required bi invalid</t>
+  </si>
+  <si>
+    <t>Empty required fields</t>
+  </si>
+  <si>
+    <t>Required validation</t>
+  </si>
+  <si>
+    <t>Practice Form bao loi khi mobile qua ngan</t>
+  </si>
+  <si>
+    <t>1. Nhap first name, last name, gender hop le`n2. Nhap mobile 5 so`n3. Click Submit</t>
+  </si>
+  <si>
+    <t>Modal khong mo va mobile field bi invalid</t>
+  </si>
+  <si>
+    <t>Mobile = 12345</t>
+  </si>
+  <si>
+    <t>Boundary mobile length</t>
+  </si>
+  <si>
+    <t>CHECK-002</t>
+  </si>
+  <si>
+    <t>Check Box</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Bo chon Home checkbox sau khi da chon</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Check Box</t>
+  </si>
+  <si>
+    <t>1. Chon Home checkbox`n2. Click Home checkbox lan nua</t>
+  </si>
+  <si>
+    <t>Ket qua selection khong con hien thi va checkbox ve false</t>
+  </si>
+  <si>
+    <t>State toggle</t>
+  </si>
+  <si>
+    <t>RADIO-002</t>
+  </si>
+  <si>
+    <t>Radio Button</t>
+  </si>
+  <si>
+    <t>Disabled radio button khong the chon</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Radio Button</t>
+  </si>
+  <si>
+    <t>1. Kiem tra option No`n2. Thu xac nhan trang thai disabled</t>
+  </si>
+  <si>
+    <t>No radio bi disabled, khong checked va khong co result moi</t>
+  </si>
+  <si>
+    <t>Option No</t>
+  </si>
+  <si>
+    <t>Disabled control</t>
+  </si>
+  <si>
+    <t>BUTTON-002</t>
+  </si>
+  <si>
+    <t>Buttons</t>
+  </si>
+  <si>
+    <t>Single click khong trigger double-click action</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Buttons</t>
+  </si>
+  <si>
+    <t>1. Single click vao Double Click Me`n2. Kiem tra message double click</t>
+  </si>
+  <si>
+    <t>Double-click message khong hien thi</t>
+  </si>
+  <si>
+    <t>Interaction specificity</t>
+  </si>
+  <si>
+    <t>UPLOAD-002</t>
+  </si>
+  <si>
+    <t>Upload and Download</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Upload file co ten chua space va ky tu dac biet</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Upload and Download</t>
+  </si>
+  <si>
+    <t>1. Upload file ten phuc tap`n2. Kiem tra uploaded path</t>
+  </si>
+  <si>
+    <t>Uploaded path hien thi dung ten file phuc tap</t>
+  </si>
+  <si>
+    <t>manual qa edge-case !@# 100.txt</t>
+  </si>
+  <si>
+    <t>Filename edge case</t>
+  </si>
+  <si>
+    <t>Search Bookstore voi keyword khong co ket qua</t>
+  </si>
+  <si>
+    <t>User da dang nhap thanh cong</t>
+  </si>
+  <si>
+    <t>1. Mo Bookstore`n2. Search keyword khong ton tai</t>
+  </si>
+  <si>
+    <t>Khong co book result nao hien thi</t>
+  </si>
+  <si>
+    <t>zzzz-no-book-123</t>
+  </si>
+  <si>
+    <t>No-result search</t>
+  </si>
+  <si>
+    <t>BROWSER-004</t>
+  </si>
+  <si>
+    <t>Mo nhieu tab moi va van giu trang goc</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Browser Windows</t>
+  </si>
+  <si>
+    <t>1. Click New Tab`n2. Verify sample page va dong tab`n3. Lap lai lan hai`n4. Quay lai trang goc</t>
+  </si>
+  <si>
+    <t>Trang Browser Windows van hien thi va khong con popup mo</t>
+  </si>
+  <si>
+    <t>2 lan New Tab</t>
+  </si>
+  <si>
+    <t>Repeated popup action</t>
+  </si>
+  <si>
+    <t>FRAME-004</t>
+  </si>
+  <si>
+    <t>Noi dung frame on dinh sau khi reload trang</t>
+  </si>
+  <si>
+    <t>1. Mo trang Frames`n2. Reload trang`n3. Doc heading trong ca hai frame</t>
+  </si>
+  <si>
+    <t>Ca hai frame van hien thi This is a sample page</t>
+  </si>
+  <si>
+    <t>Reload stability</t>
+  </si>
+  <si>
+    <t>LINK-002</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Dynamic Home link mo dung trang Home</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Links</t>
+  </si>
+  <si>
+    <t>1. Click Dynamic Home link`n2. Kiem tra tab moi`n3. Dong tab moi</t>
+  </si>
+  <si>
+    <t>Tab moi navigate ve trang Home va trang Links van hien thi</t>
+  </si>
+  <si>
+    <t>Dynamic Home link</t>
+  </si>
+  <si>
+    <t>Dynamic link</t>
+  </si>
+  <si>
+    <t>WT-002</t>
+  </si>
+  <si>
+    <t>Web Tables</t>
+  </si>
+  <si>
+    <t>Web Tables tu choi record co email sai format</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Web Tables</t>
+  </si>
+  <si>
+    <t>1. Click Add`n2. Nhap cac field hop le tru email`n3. Nhap email sai format`n4. Submit</t>
+  </si>
+  <si>
+    <t>Modal van hien thi, email invalid va record khong duoc them</t>
+  </si>
+  <si>
+    <t>not-an-email</t>
+  </si>
+  <si>
+    <t>Form validation</t>
+  </si>
+  <si>
+    <t>DYN-002</t>
+  </si>
+  <si>
+    <t>Dynamic Properties</t>
+  </si>
+  <si>
+    <t>Dynamic buttons co initial state dung truoc khi wait</t>
+  </si>
+  <si>
+    <t>Nguoi dung dang o trang Dynamic Properties</t>
+  </si>
+  <si>
+    <t>1. Mo trang Dynamic Properties`n2. Kiem tra ngay trang thai ban dau</t>
+  </si>
+  <si>
+    <t>Enable After dang disabled, Color Change chua co text-danger, Visible After dang hidden</t>
+  </si>
+  <si>
+    <t>Initial state</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1072,8 +1557,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1129,7 +1617,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1414,23 +1902,9 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="630" yWindow="540" windowWidth="27495" windowHeight="11955"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Manual Test Cases" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1439,7 +1913,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="51.7109375" customWidth="1"/>
     <col min="6" max="6" width="49.140625" customWidth="1"/>
-    <col min="7" max="7" width="59.42578125" customWidth="1"/>
+    <col min="7" max="7" width="79.85546875" customWidth="1"/>
     <col min="8" max="8" width="61.42578125" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -1447,11 +1921,9 @@
     <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>E2E Playwright Automation Framework - Danh sach test case manual</t>
-        </is>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1964,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1511,7 +1983,7 @@
       <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H3" t="s">
@@ -2556,194 +3028,958 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>FRAME-001</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Frames</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Kiem tra noi dung trong ca hai frame</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Nguoi dung dang o trang Frames</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1. Mo trang Frames`n2. Doc sample heading trong frame1 va frame2</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ca hai frame hien thi This is a sample page</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Smoke case</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>FRAME-002</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Frames</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Kiem tra kich thuoc frame lon va frame nho</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Nguoi dung dang o trang Frames</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1. Mo trang Frames`n2. So sanh bounding box cua frame1 va frame2</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Chieu rong va chieu cao cua frame thu nhat lon hon frame thu hai</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>FRAME-003</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nested Frames</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Kiem tra noi dung trong nested frames</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Nguoi dung dang o trang Nested Frames</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1. Mo trang Nested Frames`n2. Doc noi dung parent frame`n3. Doc noi dung child iframe</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Parent frame hien thi Parent frame va child iframe hien thi Child Iframe</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Dung nested frameLocator</t>
-        </is>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>185</v>
+      </c>
+      <c r="B31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>187</v>
+      </c>
+      <c r="F31" t="s">
+        <v>188</v>
+      </c>
+      <c r="G31" t="s">
+        <v>189</v>
+      </c>
+      <c r="H31" t="s">
+        <v>190</v>
+      </c>
+      <c r="I31" t="s">
+        <v>143</v>
+      </c>
+      <c r="J31" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" t="s">
+        <v>195</v>
+      </c>
+      <c r="I32" t="s">
+        <v>143</v>
+      </c>
+      <c r="J32" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F33" t="s">
+        <v>199</v>
+      </c>
+      <c r="G33" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" t="s">
+        <v>201</v>
+      </c>
+      <c r="I33" t="s">
+        <v>143</v>
+      </c>
+      <c r="J33" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" t="s">
+        <v>205</v>
+      </c>
+      <c r="G34" t="s">
+        <v>206</v>
+      </c>
+      <c r="H34" t="s">
+        <v>207</v>
+      </c>
+      <c r="I34" t="s">
+        <v>208</v>
+      </c>
+      <c r="J34" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" t="s">
+        <v>213</v>
+      </c>
+      <c r="H35" t="s">
+        <v>214</v>
+      </c>
+      <c r="I35" t="s">
+        <v>215</v>
+      </c>
+      <c r="J35" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" t="s">
+        <v>219</v>
+      </c>
+      <c r="F36" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" t="s">
+        <v>221</v>
+      </c>
+      <c r="H36" t="s">
+        <v>222</v>
+      </c>
+      <c r="I36" t="s">
+        <v>223</v>
+      </c>
+      <c r="J36" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s">
+        <v>22</v>
+      </c>
+      <c r="L36" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s">
+        <v>211</v>
+      </c>
+      <c r="E37" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" t="s">
+        <v>230</v>
+      </c>
+      <c r="I37" t="s">
+        <v>231</v>
+      </c>
+      <c r="J37" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>233</v>
+      </c>
+      <c r="B38" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>234</v>
+      </c>
+      <c r="F38" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" t="s">
+        <v>235</v>
+      </c>
+      <c r="H38" t="s">
+        <v>236</v>
+      </c>
+      <c r="I38" t="s">
+        <v>237</v>
+      </c>
+      <c r="J38" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>241</v>
+      </c>
+      <c r="F39" t="s">
+        <v>242</v>
+      </c>
+      <c r="G39" t="s">
+        <v>243</v>
+      </c>
+      <c r="H39" t="s">
+        <v>244</v>
+      </c>
+      <c r="I39" t="s">
+        <v>143</v>
+      </c>
+      <c r="J39" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s">
+        <v>211</v>
+      </c>
+      <c r="E40" t="s">
+        <v>247</v>
+      </c>
+      <c r="F40" t="s">
+        <v>242</v>
+      </c>
+      <c r="G40" t="s">
+        <v>248</v>
+      </c>
+      <c r="H40" t="s">
+        <v>249</v>
+      </c>
+      <c r="I40" t="s">
+        <v>250</v>
+      </c>
+      <c r="J40" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L40" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>252</v>
+      </c>
+      <c r="B41" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F41" t="s">
+        <v>255</v>
+      </c>
+      <c r="G41" t="s">
+        <v>256</v>
+      </c>
+      <c r="H41" t="s">
+        <v>257</v>
+      </c>
+      <c r="I41" t="s">
+        <v>143</v>
+      </c>
+      <c r="J41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s">
+        <v>192</v>
+      </c>
+      <c r="E42" t="s">
+        <v>260</v>
+      </c>
+      <c r="F42" t="s">
+        <v>255</v>
+      </c>
+      <c r="G42" t="s">
+        <v>261</v>
+      </c>
+      <c r="H42" t="s">
+        <v>257</v>
+      </c>
+      <c r="I42" t="s">
+        <v>143</v>
+      </c>
+      <c r="J42" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" t="s">
+        <v>263</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" t="s">
+        <v>264</v>
+      </c>
+      <c r="F43" t="s">
+        <v>265</v>
+      </c>
+      <c r="G43" t="s">
+        <v>266</v>
+      </c>
+      <c r="H43" t="s">
+        <v>267</v>
+      </c>
+      <c r="I43" t="s">
+        <v>268</v>
+      </c>
+      <c r="J43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" t="s">
+        <v>263</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" t="s">
+        <v>270</v>
+      </c>
+      <c r="F44" t="s">
+        <v>265</v>
+      </c>
+      <c r="G44" t="s">
+        <v>271</v>
+      </c>
+      <c r="H44" t="s">
+        <v>272</v>
+      </c>
+      <c r="I44" t="s">
+        <v>273</v>
+      </c>
+      <c r="J44" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>275</v>
+      </c>
+      <c r="F45" t="s">
+        <v>265</v>
+      </c>
+      <c r="G45" t="s">
+        <v>276</v>
+      </c>
+      <c r="H45" t="s">
+        <v>277</v>
+      </c>
+      <c r="I45" t="s">
+        <v>278</v>
+      </c>
+      <c r="J45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>280</v>
+      </c>
+      <c r="B46" t="s">
+        <v>281</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" t="s">
+        <v>283</v>
+      </c>
+      <c r="F46" t="s">
+        <v>284</v>
+      </c>
+      <c r="G46" t="s">
+        <v>285</v>
+      </c>
+      <c r="H46" t="s">
+        <v>286</v>
+      </c>
+      <c r="I46" t="s">
+        <v>143</v>
+      </c>
+      <c r="J46" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>288</v>
+      </c>
+      <c r="B47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" t="s">
+        <v>290</v>
+      </c>
+      <c r="F47" t="s">
+        <v>291</v>
+      </c>
+      <c r="G47" t="s">
+        <v>292</v>
+      </c>
+      <c r="H47" t="s">
+        <v>293</v>
+      </c>
+      <c r="I47" t="s">
+        <v>294</v>
+      </c>
+      <c r="J47" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" t="s">
+        <v>22</v>
+      </c>
+      <c r="L47" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B48" t="s">
+        <v>297</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>298</v>
+      </c>
+      <c r="F48" t="s">
+        <v>299</v>
+      </c>
+      <c r="G48" t="s">
+        <v>300</v>
+      </c>
+      <c r="H48" t="s">
+        <v>301</v>
+      </c>
+      <c r="I48" t="s">
+        <v>143</v>
+      </c>
+      <c r="J48" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L48" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>303</v>
+      </c>
+      <c r="B49" t="s">
+        <v>304</v>
+      </c>
+      <c r="C49" t="s">
+        <v>305</v>
+      </c>
+      <c r="D49" t="s">
+        <v>211</v>
+      </c>
+      <c r="E49" t="s">
+        <v>306</v>
+      </c>
+      <c r="F49" t="s">
+        <v>307</v>
+      </c>
+      <c r="G49" t="s">
+        <v>308</v>
+      </c>
+      <c r="H49" t="s">
+        <v>309</v>
+      </c>
+      <c r="I49" t="s">
+        <v>310</v>
+      </c>
+      <c r="J49" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" t="s">
+        <v>312</v>
+      </c>
+      <c r="F50" t="s">
+        <v>313</v>
+      </c>
+      <c r="G50" t="s">
+        <v>314</v>
+      </c>
+      <c r="H50" t="s">
+        <v>315</v>
+      </c>
+      <c r="I50" t="s">
+        <v>316</v>
+      </c>
+      <c r="J50" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" t="s">
+        <v>22</v>
+      </c>
+      <c r="L50" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>318</v>
+      </c>
+      <c r="B51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" t="s">
+        <v>282</v>
+      </c>
+      <c r="E51" t="s">
+        <v>319</v>
+      </c>
+      <c r="F51" t="s">
+        <v>320</v>
+      </c>
+      <c r="G51" t="s">
+        <v>321</v>
+      </c>
+      <c r="H51" t="s">
+        <v>322</v>
+      </c>
+      <c r="I51" t="s">
+        <v>323</v>
+      </c>
+      <c r="J51" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" t="s">
+        <v>22</v>
+      </c>
+      <c r="L51" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>325</v>
+      </c>
+      <c r="B52" t="s">
+        <v>186</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>282</v>
+      </c>
+      <c r="E52" t="s">
+        <v>326</v>
+      </c>
+      <c r="F52" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" t="s">
+        <v>327</v>
+      </c>
+      <c r="H52" t="s">
+        <v>328</v>
+      </c>
+      <c r="I52" t="s">
+        <v>143</v>
+      </c>
+      <c r="J52" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s">
+        <v>22</v>
+      </c>
+      <c r="L52" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>330</v>
+      </c>
+      <c r="B53" t="s">
+        <v>331</v>
+      </c>
+      <c r="C53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" t="s">
+        <v>282</v>
+      </c>
+      <c r="E53" t="s">
+        <v>332</v>
+      </c>
+      <c r="F53" t="s">
+        <v>333</v>
+      </c>
+      <c r="G53" t="s">
+        <v>334</v>
+      </c>
+      <c r="H53" t="s">
+        <v>335</v>
+      </c>
+      <c r="I53" t="s">
+        <v>336</v>
+      </c>
+      <c r="J53" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s">
+        <v>22</v>
+      </c>
+      <c r="L53" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>338</v>
+      </c>
+      <c r="B54" t="s">
+        <v>339</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" t="s">
+        <v>340</v>
+      </c>
+      <c r="F54" t="s">
+        <v>341</v>
+      </c>
+      <c r="G54" t="s">
+        <v>342</v>
+      </c>
+      <c r="H54" t="s">
+        <v>343</v>
+      </c>
+      <c r="I54" t="s">
+        <v>344</v>
+      </c>
+      <c r="J54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s">
+        <v>22</v>
+      </c>
+      <c r="L54" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>346</v>
+      </c>
+      <c r="B55" t="s">
+        <v>347</v>
+      </c>
+      <c r="C55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" t="s">
+        <v>282</v>
+      </c>
+      <c r="E55" t="s">
+        <v>348</v>
+      </c>
+      <c r="F55" t="s">
+        <v>349</v>
+      </c>
+      <c r="G55" t="s">
+        <v>350</v>
+      </c>
+      <c r="H55" t="s">
+        <v>351</v>
+      </c>
+      <c r="I55" t="s">
+        <v>143</v>
+      </c>
+      <c r="J55" t="s">
+        <v>21</v>
+      </c>
+      <c r="K55" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L33"/>
+  <autoFilter ref="A2:L55"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Manual_Test_Cases.xlsx
+++ b/docs/Manual_Test_Cases.xlsx
@@ -1,19 +1,41 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="630" yWindow="540" windowWidth="27495" windowHeight="11955"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Manual Test Cases" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Manual Test Cases</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>14.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:title>Manual Test Cases</dc:title>
+  <dc:creator>Codex</dc:creator>
+  <cp:lastModifiedBy>Windows User</cp:lastModifiedBy>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-06-16T07:51:23Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="353">
   <si>
     <t>Test Case ID</t>
@@ -1077,7 +1099,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1557,10 +1579,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1617,7 +1648,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1902,2084 +1933,2983 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="630" yWindow="540" windowWidth="27495" windowHeight="11955"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Manual Test Cases" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="51.7109375" customWidth="1"/>
-    <col min="6" max="6" width="49.140625" customWidth="1"/>
-    <col min="7" max="7" width="79.85546875" customWidth="1"/>
-    <col min="8" max="8" width="61.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="48" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25" ht="28" customHeight="1">
+      <c r="A1" t="s" s="2">
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25" ht="32" customHeight="1">
+      <c r="A2" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="3">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="3">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="3">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="3">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="3">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="3">
         <v>7</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="3">
         <v>8</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="3">
         <v>9</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="3">
         <v>10</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="4">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="4">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="4">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" t="s" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A4" t="s" s="4">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="4">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="4">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="4">
         <v>28</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="4">
         <v>29</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A5" t="s" s="4">
         <v>31</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="4">
         <v>33</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="4">
         <v>34</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="4">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="4">
         <v>36</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="4">
         <v>37</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" t="s" s="4">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A6" t="s" s="4">
         <v>41</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="4">
         <v>42</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="4">
         <v>34</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="4">
         <v>43</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" t="s" s="4">
         <v>36</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="4">
         <v>44</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" t="s" s="4">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A7" t="s" s="4">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="4">
         <v>46</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="4">
         <v>47</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" t="s" s="4">
         <v>48</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" t="s" s="4">
         <v>49</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" t="s" s="4">
         <v>50</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A8" t="s" s="4">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="4">
         <v>52</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="4">
         <v>53</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" t="s" s="4">
         <v>54</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" t="s" s="4">
         <v>55</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" t="s" s="4">
         <v>56</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A9" t="s" s="4">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="4">
         <v>58</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="4">
         <v>59</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" t="s" s="4">
         <v>60</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" t="s" s="4">
         <v>61</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" t="s" s="4">
         <v>62</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A10" t="s" s="4">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="4">
         <v>64</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="4">
         <v>59</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" t="s" s="4">
         <v>65</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" t="s" s="4">
         <v>66</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" t="s" s="4">
         <v>67</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A11" t="s" s="4">
         <v>68</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="4">
         <v>70</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="4">
         <v>71</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" t="s" s="4">
         <v>72</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" t="s" s="4">
         <v>73</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" t="s" s="4">
         <v>74</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" t="s" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A12" t="s" s="4">
         <v>75</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="4">
         <v>76</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="s" s="4">
         <v>77</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" t="s" s="4">
         <v>78</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" t="s" s="4">
         <v>79</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" t="s" s="4">
         <v>80</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" t="s" s="4">
         <v>81</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" t="s" s="4">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A13" t="s" s="4">
         <v>83</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="4">
         <v>84</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="4">
         <v>85</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" t="s" s="4">
         <v>86</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" t="s" s="4">
         <v>87</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" t="s" s="4">
         <v>80</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A14" t="s" s="4">
         <v>88</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="4">
         <v>89</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="4">
         <v>90</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" t="s" s="4">
         <v>91</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" t="s" s="4">
         <v>92</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" t="s" s="4">
         <v>80</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A15" t="s" s="4">
         <v>93</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="4">
         <v>94</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="s" s="4">
         <v>71</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" t="s" s="4">
         <v>95</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" t="s" s="4">
         <v>96</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" t="s" s="4">
         <v>97</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A16" t="s" s="4">
         <v>98</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="4">
         <v>99</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="4">
         <v>100</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" t="s" s="4">
         <v>101</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" t="s" s="4">
         <v>102</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" t="s" s="4">
         <v>103</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A17" t="s" s="4">
         <v>104</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="4">
         <v>105</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="4">
         <v>106</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="4">
         <v>107</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" t="s" s="4">
         <v>108</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" t="s" s="4">
         <v>109</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" t="s" s="4">
         <v>110</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" t="s" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A18" t="s" s="4">
         <v>111</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="4">
         <v>105</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="4">
         <v>112</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" t="s" s="4">
         <v>113</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" t="s" s="4">
         <v>114</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" t="s" s="4">
         <v>115</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" t="s" s="4">
         <v>116</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A19" t="s" s="4">
         <v>117</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="4">
         <v>105</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" t="s" s="4">
         <v>118</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" t="s" s="4">
         <v>107</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" t="s" s="4">
         <v>119</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" t="s" s="4">
         <v>120</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" t="s" s="4">
         <v>121</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A20" t="s" s="4">
         <v>122</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="4">
         <v>105</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="4">
         <v>123</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="4">
         <v>107</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" t="s" s="4">
         <v>124</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" t="s" s="4">
         <v>125</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" t="s" s="4">
         <v>126</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A21" t="s" s="4">
         <v>127</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="4">
         <v>105</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="4">
         <v>128</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="s" s="4">
         <v>107</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" t="s" s="4">
         <v>129</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" t="s" s="4">
         <v>130</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" t="s" s="4">
         <v>131</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A22" t="s" s="4">
         <v>132</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="4">
         <v>105</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="4">
         <v>133</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" t="s" s="4">
         <v>107</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" t="s" s="4">
         <v>134</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" t="s" s="4">
         <v>135</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" t="s" s="4">
         <v>136</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A23" t="s" s="4">
         <v>137</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="4">
         <v>138</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" t="s" s="4">
         <v>139</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" t="s" s="4">
         <v>140</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="4">
         <v>141</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" t="s" s="4">
         <v>142</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" t="s" s="4">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A24" t="s" s="4">
         <v>145</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="4">
         <v>138</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" t="s" s="4">
         <v>146</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" t="s" s="4">
         <v>140</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" t="s" s="4">
         <v>147</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" t="s" s="4">
         <v>148</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" t="s" s="4">
         <v>144</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A25" t="s" s="4">
         <v>149</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="4">
         <v>138</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" t="s" s="4">
         <v>150</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" t="s" s="4">
         <v>140</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" t="s" s="4">
         <v>151</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" t="s" s="4">
         <v>152</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A26" t="s" s="4">
         <v>153</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="4">
         <v>138</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" t="s" s="4">
         <v>154</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" t="s" s="4">
         <v>155</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" t="s" s="4">
         <v>156</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" t="s" s="4">
         <v>157</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A27" t="s" s="4">
         <v>158</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="4">
         <v>159</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" t="s" s="4">
         <v>160</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" t="s" s="4">
         <v>161</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" t="s" s="4">
         <v>163</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" t="s" s="4">
         <v>164</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" t="s" s="4">
         <v>165</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" t="s" s="4">
         <v>166</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L27" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A28" t="s" s="4">
         <v>167</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="4">
         <v>159</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" t="s" s="4">
         <v>160</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" t="s" s="4">
         <v>168</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" t="s" s="4">
         <v>169</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" t="s" s="4">
         <v>170</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" t="s" s="4">
         <v>171</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" t="s" s="4">
         <v>165</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K28" t="s" s="4">
         <v>166</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A29" t="s" s="4">
         <v>172</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="4">
         <v>159</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" t="s" s="4">
         <v>160</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" t="s" s="4">
         <v>173</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" t="s" s="4">
         <v>174</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" t="s" s="4">
         <v>175</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" t="s" s="4">
         <v>176</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" t="s" s="4">
         <v>177</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" t="s" s="4">
         <v>165</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" t="s" s="4">
         <v>166</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A30" t="s" s="4">
         <v>178</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="4">
         <v>159</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" t="s" s="4">
         <v>160</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" t="s" s="4">
         <v>179</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" t="s" s="4">
         <v>180</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" t="s" s="4">
         <v>181</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" t="s" s="4">
         <v>182</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" t="s" s="4">
         <v>183</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" t="s" s="4">
         <v>165</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30" t="s" s="4">
         <v>166</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L30" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A31" t="s" s="4">
         <v>185</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="4">
         <v>186</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" t="s" s="4">
         <v>187</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" t="s" s="4">
         <v>188</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" t="s" s="4">
         <v>189</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" t="s" s="4">
         <v>190</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K31" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L31" t="s" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A32" t="s" s="4">
         <v>191</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="4">
         <v>186</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" t="s" s="4">
         <v>192</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" t="s" s="4">
         <v>193</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" t="s" s="4">
         <v>188</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" t="s" s="4">
         <v>194</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" t="s" s="4">
         <v>195</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L32" t="s" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A33" t="s" s="4">
         <v>196</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="4">
         <v>197</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" t="s" s="4">
         <v>198</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" t="s" s="4">
         <v>199</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" t="s" s="4">
         <v>200</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" t="s" s="4">
         <v>201</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K33" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L33" t="s" s="4">
         <v>202</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A34" t="inlineStr" s="4">
+        <is>
+          <t>AUTH-011</t>
+        </is>
+      </c>
+      <c r="B34" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" t="s" s="4">
         <v>203</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" t="s" s="4">
         <v>204</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" t="s" s="4">
         <v>205</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" t="s" s="4">
         <v>206</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" t="s" s="4">
         <v>207</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" t="s" s="4">
         <v>208</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L34" t="s" s="4">
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>210</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A35" t="inlineStr" s="4">
+        <is>
+          <t>AUTH-012</t>
+        </is>
+      </c>
+      <c r="B35" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" t="s" s="4">
         <v>211</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" t="s" s="4">
         <v>212</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" t="s" s="4">
         <v>205</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" t="s" s="4">
         <v>213</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" t="s" s="4">
         <v>214</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" t="s" s="4">
         <v>215</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L35" t="s" s="4">
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>217</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A36" t="inlineStr" s="4">
+        <is>
+          <t>AUTH-013</t>
+        </is>
+      </c>
+      <c r="B36" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" t="s" s="4">
         <v>218</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" t="s" s="4">
         <v>219</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" t="s" s="4">
         <v>220</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" t="s" s="4">
         <v>221</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" t="s" s="4">
         <v>222</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" t="s" s="4">
         <v>223</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K36" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" t="s" s="4">
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A37" t="s" s="4">
         <v>225</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="4">
         <v>226</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" t="s" s="4">
         <v>211</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" t="s" s="4">
         <v>227</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" t="s" s="4">
         <v>228</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" t="s" s="4">
         <v>229</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" t="s" s="4">
         <v>230</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" t="s" s="4">
         <v>231</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K37" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L37" t="s">
+      <c r="L37" t="s" s="4">
         <v>232</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A38" t="s" s="4">
         <v>233</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="4">
         <v>226</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" t="s" s="4">
         <v>234</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" t="s" s="4">
         <v>228</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" t="s" s="4">
         <v>235</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" t="s" s="4">
         <v>236</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" t="s" s="4">
         <v>237</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K38" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L38" t="s" s="4">
         <v>238</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A39" t="s" s="4">
         <v>239</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="4">
         <v>240</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" t="s" s="4">
         <v>241</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" t="s" s="4">
         <v>242</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" t="s" s="4">
         <v>243</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" t="s" s="4">
         <v>244</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K39" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L39" t="s">
+      <c r="L39" t="s" s="4">
         <v>245</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A40" t="s" s="4">
         <v>246</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="4">
         <v>240</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" t="s" s="4">
         <v>211</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" t="s" s="4">
         <v>247</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" t="s" s="4">
         <v>242</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" t="s" s="4">
         <v>248</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" t="s" s="4">
         <v>249</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" t="s" s="4">
         <v>250</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" t="s" s="4">
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A41" t="s" s="4">
         <v>252</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="4">
         <v>253</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" t="s" s="4">
         <v>192</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" t="s" s="4">
         <v>254</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" t="s" s="4">
         <v>255</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" t="s" s="4">
         <v>256</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" t="s" s="4">
         <v>257</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K41" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L41" t="s">
+      <c r="L41" t="s" s="4">
         <v>258</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A42" t="s" s="4">
         <v>259</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="4">
         <v>253</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" t="s" s="4">
         <v>192</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" t="s" s="4">
         <v>260</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" t="s" s="4">
         <v>255</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" t="s" s="4">
         <v>261</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" t="s" s="4">
         <v>257</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L42" t="s" s="4">
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A43" t="inlineStr" s="4">
+        <is>
+          <t>FORM-007</t>
+        </is>
+      </c>
+      <c r="B43" t="s" s="4">
         <v>263</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" t="s" s="4">
         <v>211</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" t="s" s="4">
         <v>264</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" t="s" s="4">
         <v>265</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" t="s" s="4">
         <v>266</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" t="s" s="4">
         <v>267</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" t="s" s="4">
         <v>268</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" t="s" s="4">
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>117</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A44" t="inlineStr" s="4">
+        <is>
+          <t>FORM-008</t>
+        </is>
+      </c>
+      <c r="B44" t="s" s="4">
         <v>263</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" t="s" s="4">
         <v>270</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" t="s" s="4">
         <v>265</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" t="s" s="4">
         <v>271</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" t="s" s="4">
         <v>272</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" t="s" s="4">
         <v>273</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L44" t="s" s="4">
         <v>274</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>122</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A45" t="inlineStr" s="4">
+        <is>
+          <t>FORM-009</t>
+        </is>
+      </c>
+      <c r="B45" t="s" s="4">
         <v>263</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" t="s" s="4">
         <v>275</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" t="s" s="4">
         <v>265</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" t="s" s="4">
         <v>276</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" t="s" s="4">
         <v>277</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" t="s" s="4">
         <v>278</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" t="s" s="4">
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A46" t="s" s="4">
         <v>280</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="4">
         <v>281</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" t="s" s="4">
         <v>282</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" t="s" s="4">
         <v>283</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" t="s" s="4">
         <v>284</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" t="s" s="4">
         <v>285</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" t="s" s="4">
         <v>286</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K46" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" t="s" s="4">
         <v>287</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A47" t="s" s="4">
         <v>288</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="4">
         <v>289</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" t="s" s="4">
         <v>290</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" t="s" s="4">
         <v>291</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" t="s" s="4">
         <v>292</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" t="s" s="4">
         <v>293</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" t="s" s="4">
         <v>294</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" t="s" s="4">
         <v>295</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A48" t="s" s="4">
         <v>296</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="4">
         <v>297</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" t="s" s="4">
         <v>298</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" t="s" s="4">
         <v>299</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" t="s" s="4">
         <v>300</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" t="s" s="4">
         <v>301</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" t="s" s="4">
         <v>302</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A49" t="s" s="4">
         <v>303</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="4">
         <v>304</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" t="s" s="4">
         <v>305</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" t="s" s="4">
         <v>211</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" t="s" s="4">
         <v>306</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" t="s" s="4">
         <v>307</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" t="s" s="4">
         <v>308</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" t="s" s="4">
         <v>309</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" t="s" s="4">
         <v>310</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K49" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L49" t="s" s="4">
         <v>311</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B50" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A50" t="inlineStr" s="4">
+        <is>
+          <t>BOOK-007</t>
+        </is>
+      </c>
+      <c r="B50" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" t="s" s="4">
         <v>312</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" t="s" s="4">
         <v>313</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" t="s" s="4">
         <v>314</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" t="s" s="4">
         <v>315</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" t="s" s="4">
         <v>316</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K50" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" t="s" s="4">
         <v>317</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A51" t="s" s="4">
         <v>318</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="4">
         <v>138</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" t="s" s="4">
         <v>282</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" t="s" s="4">
         <v>319</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" t="s" s="4">
         <v>320</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" t="s" s="4">
         <v>321</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" t="s" s="4">
         <v>322</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" t="s" s="4">
         <v>323</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K51" t="s">
+      <c r="K51" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L51" t="s" s="4">
         <v>324</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A52" t="s" s="4">
         <v>325</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="4">
         <v>186</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" t="s" s="4">
         <v>282</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" t="s" s="4">
         <v>326</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" t="s" s="4">
         <v>188</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" t="s" s="4">
         <v>327</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" t="s" s="4">
         <v>328</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K52" t="s">
+      <c r="K52" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L52" t="s" s="4">
         <v>329</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A53" t="s" s="4">
         <v>330</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="4">
         <v>331</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" t="s" s="4">
         <v>282</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" t="s" s="4">
         <v>332</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" t="s" s="4">
         <v>333</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" t="s" s="4">
         <v>334</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" t="s" s="4">
         <v>335</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" t="s" s="4">
         <v>336</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K53" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L53" t="s">
+      <c r="L53" t="s" s="4">
         <v>337</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A54" t="s" s="4">
         <v>338</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="4">
         <v>339</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" t="s" s="4">
         <v>340</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" t="s" s="4">
         <v>341</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G54" t="s" s="4">
         <v>342</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" t="s" s="4">
         <v>343</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" t="s" s="4">
         <v>344</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L54" t="s" s="4">
         <v>345</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25" ht="52" customHeight="1">
+      <c r="A55" t="s" s="4">
         <v>346</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="4">
         <v>347</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" t="s" s="4">
         <v>282</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" t="s" s="4">
         <v>348</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" t="s" s="4">
         <v>349</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G55" t="s" s="4">
         <v>350</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" t="s" s="4">
         <v>351</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" t="s" s="4">
         <v>143</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K55" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="L55" t="s">
+      <c r="L55" t="s" s="4">
         <v>352</v>
       </c>
     </row>
+    <row r="56" spans="1:12" ht="58" customHeight="1">
+      <c r="A56" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Accordian</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="4">
+        <is>
+          <t>Kiem tra expand/collapse cac section Accordian</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Accordian</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr" s="4">
+        <is>
+          <t>1. Mo trang Accordian`n2. Xac nhan section dau tien expanded`n3. Mo section thu hai`n4. Mo section thu ba</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr" s="4">
+        <is>
+          <t>Noi dung cua tung section duoc hien thi dung khi expanded</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr" s="4">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @accordian</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="58" customHeight="1">
+      <c r="A57" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-002</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Auto Complete</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="4">
+        <is>
+          <t>Chon multi-value va single-value trong Auto Complete</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Auto Complete</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr" s="4">
+        <is>
+          <t>1. Nhap Red va Green vao multi color`n2. Nhap Blue vao single color</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr" s="4">
+        <is>
+          <t>Red, Green va Blue duoc hien thi trong dung control</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr" s="4">
+        <is>
+          <t>Red, Green, Blue</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @auto-complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="58" customHeight="1">
+      <c r="A58" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-003</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Date Picker</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="4">
+        <is>
+          <t>Cap nhat Date Picker va Date Time Picker</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Date Picker</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr" s="4">
+        <is>
+          <t>1. Nhap date 12/31/2026`n2. Nhap datetime December 31, 2026 11:45 PM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr" s="4">
+        <is>
+          <t>Hai input hien thi dung gia tri moi</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr" s="4">
+        <is>
+          <t>12/31/2026; December 31, 2026 11:45 PM</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @date-picker</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="58" customHeight="1">
+      <c r="A59" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-004</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Slider</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="4">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="4">
+        <is>
+          <t>Di chuyen Slider toi gia tri 75</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Slider</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr" s="4">
+        <is>
+          <t>1. Set slider value = 75`n2. Kiem tra output value</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr" s="4">
+        <is>
+          <t>Slider value hien thi 75</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr" s="4">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @slider</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="58" customHeight="1">
+      <c r="A60" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-005</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Progress Bar</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="4">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="4">
+        <is>
+          <t>Start progress bar den 100 va reset ve 0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Progress Bar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr" s="4">
+        <is>
+          <t>1. Click Start`n2. Cho progress dat 100%`n3. Click Reset</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr" s="4">
+        <is>
+          <t>Progress bar dat 100%, sau reset ve 0%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr" s="4">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @progress-bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="58" customHeight="1">
+      <c r="A61" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-006</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Tabs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="4">
+        <is>
+          <t>Chuyen giua cac tab What, Origin, Use</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Tabs</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr" s="4">
+        <is>
+          <t>1. Xac nhan tab What`n2. Click Origin`n3. Click Use</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr" s="4">
+        <is>
+          <t>Noi dung tab tuong ung duoc hien thi va tab active thay doi dung</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr" s="4">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="58" customHeight="1">
+      <c r="A62" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-007</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Tool Tips</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="4">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="4">
+        <is>
+          <t>Hien thi tooltip cho button va input</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Tool Tips</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr" s="4">
+        <is>
+          <t>1. Hover button`n2. Kiem tra tooltip`n3. Hover input`n4. Kiem tra tooltip</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr" s="4">
+        <is>
+          <t>Tooltip dung text hien thi cho button va input</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr" s="4">
+        <is>
+          <t>Button/input tooltip</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @tool-tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="58" customHeight="1">
+      <c r="A63" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-008</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Menu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="4">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="4">
+        <is>
+          <t>Hover nested menu toi Sub Sub Item</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Menu</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr" s="4">
+        <is>
+          <t>1. Hover Main Item 2`n2. Hover SUB SUB LIST`n3. Kiem tra sub sub items</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr" s="4">
+        <is>
+          <t>Sub Sub Item 1 va Sub Sub Item 2 hien thi</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr" s="4">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="58" customHeight="1">
+      <c r="A64" t="inlineStr" s="4">
+        <is>
+          <t>WIDGET-009</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="4">
+        <is>
+          <t>Widgets - Select Menu</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="4">
+        <is>
+          <t>Chon value trong Select Menu va multi-select cars</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Select Menu</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr" s="4">
+        <is>
+          <t>1. Chon Group 1 option 1`n2. Chon Aqua trong old select`n3. Chon Volvo va Saab trong cars</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr" s="4">
+        <is>
+          <t>Tat ca gia tri da chon hien thi dung</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr" s="4">
+        <is>
+          <t>Group 1 option 1; Aqua; Volvo/Saab</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr" s="4">
+        <is>
+          <t>@widgets @select-menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="58" customHeight="1">
+      <c r="A65" t="inlineStr" s="4">
+        <is>
+          <t>INT-001</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="4">
+        <is>
+          <t>Interactions - Sortable</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="4">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="4">
+        <is>
+          <t>Kiem tra Sortable list va grid san sang drag</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Sortable</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr" s="4">
+        <is>
+          <t>1. Mo trang Sortable`n2. Kiem tra List co 6 item`n3. Chuyen sang Grid`n4. Kiem tra Grid co 9 item draggable</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr" s="4">
+        <is>
+          <t>List/Grid render day du item va item co draggable=true</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr" s="4">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr" s="4">
+        <is>
+          <t>@interactions @sortable</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="58" customHeight="1">
+      <c r="A66" t="inlineStr" s="4">
+        <is>
+          <t>INT-002</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="4">
+        <is>
+          <t>Interactions - Selectable</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="4">
+        <is>
+          <t>Chon nhieu item trong Selectable list</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Selectable</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr" s="4">
+        <is>
+          <t>1. Click item 1`n2. Click item 3`n3. Kiem tra class active</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr" s="4">
+        <is>
+          <t>Item 1 va item 3 duoc highlight, item 2 khong active</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr" s="4">
+        <is>
+          <t>Cras justo odio; Morbi leo risus</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr" s="4">
+        <is>
+          <t>@interactions @selectable</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="58" customHeight="1">
+      <c r="A67" t="inlineStr" s="4">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="4">
+        <is>
+          <t>Interactions - Resizable</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="4">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="4">
+        <is>
+          <t>Resize restricted box tang kich thuoc</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Resizable</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr" s="4">
+        <is>
+          <t>1. Ghi nhan kich thuoc ban dau`n2. Keo resize handle`n3. Kiem tra kich thuoc moi</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr" s="4">
+        <is>
+          <t>Width va height cua box tang so voi ban dau</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr" s="4">
+        <is>
+          <t>Resize +120/+80</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr" s="4">
+        <is>
+          <t>@interactions @resizable</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="58" customHeight="1">
+      <c r="A68" t="inlineStr" s="4">
+        <is>
+          <t>INT-004</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="4">
+        <is>
+          <t>Interactions - Droppable</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="4">
+        <is>
+          <t>Drag item vao drop area</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Droppable</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr" s="4">
+        <is>
+          <t>1. Keo Drag Me vao Drop Here`n2. Tha chuot trong drop area</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr" s="4">
+        <is>
+          <t>Drop area hien thi Dropped! va co highlight state</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr" s="4">
+        <is>
+          <t>Simple tab</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr" s="4">
+        <is>
+          <t>@interactions @droppable</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="58" customHeight="1">
+      <c r="A69" t="inlineStr" s="4">
+        <is>
+          <t>INT-005</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="4">
+        <is>
+          <t>Interactions - Dragabble</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="4">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="4">
+        <is>
+          <t>Drag simple drag box sang vi tri moi</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="4">
+        <is>
+          <t>Nguoi dung dang o trang Dragabble</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr" s="4">
+        <is>
+          <t>1. Ghi nhan vi tri ban dau`n2. Keo drag box sang vi tri moi`n3. Kiem tra displacement</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr" s="4">
+        <is>
+          <t>Drag box thay doi vi tri so voi ban dau</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr" s="4">
+        <is>
+          <t>Simple tab</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr" s="4">
+        <is>
+          <t>@interactions @dragabble</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L55"/>
+  <autoFilter ref="A2:L69"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Manual_Test_Cases.xlsx
+++ b/docs/Manual_Test_Cases.xlsx
@@ -1949,7 +1949,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4905,8 +4905,520 @@
         </is>
       </c>
     </row>
+    <row r="70" spans="1:12" ht="72" customHeight="1">
+      <c r="A70" t="inlineStr" s="4">
+        <is>
+          <t>API-001</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="4">
+        <is>
+          <t>Book Store API</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="4">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="4">
+        <is>
+          <t>Lay danh sach sach tu Book Store API</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="4">
+        <is>
+          <t>DemoQA API dang hoat dong</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Gui GET /BookStore/v1/Books
+2. Kiem tra HTTP status
+3. Kiem tra danh sach books</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr" s="4">
+        <is>
+          <t>Tra ve 200; books la mang khong rong; moi sach co isbn, title va author</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr" s="4">
+        <is>
+          <t>GET /BookStore/v1/Books</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api @smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="72" customHeight="1">
+      <c r="A71" t="inlineStr" s="4">
+        <is>
+          <t>API-002</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="4">
+        <is>
+          <t>Book Store API</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="4">
+        <is>
+          <t>Lay chi tiet sach theo ISBN hop le</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="4">
+        <is>
+          <t>Catalog co it nhat mot sach</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Lay ISBN dau tien tu catalog
+2. Gui GET /BookStore/v1/Book voi ISBN
+3. So sanh response voi catalog</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr" s="4">
+        <is>
+          <t>Tra ve 200; isbn va title khop voi sach da yeu cau</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr" s="4">
+        <is>
+          <t>ISBN dau tien trong catalog</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="72" customHeight="1">
+      <c r="A72" t="inlineStr" s="4">
+        <is>
+          <t>API-003</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="4">
+        <is>
+          <t>Book Store API</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="4">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="4">
+        <is>
+          <t>Tu choi ISBN khong hop le</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="4">
+        <is>
+          <t>DemoQA API dang hoat dong</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Gui GET /BookStore/v1/Book
+2. Truyen ISBN=invalid-isbn
+3. Kiem tra HTTP status</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr" s="4">
+        <is>
+          <t>Tra ve 400 cho ISBN khong hop le</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr" s="4">
+        <is>
+          <t>ISBN: invalid-isbn</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api @negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="72" customHeight="1">
+      <c r="A73" t="inlineStr" s="4">
+        <is>
+          <t>API-004</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="4">
+        <is>
+          <t>Account API</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="4">
+        <is>
+          <t>Xac thuc credentials cua API user hop le</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="4">
+        <is>
+          <t>API user moi da duoc tao va token da duoc sinh</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Gui POST /Account/v1/Authorized
+2. Truyen userName va password hop le
+3. Kiem tra response</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr" s="4">
+        <is>
+          <t>Tra ve 200 va response boolean true</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr" s="4">
+        <is>
+          <t>Tai khoan duoc tao dong trong test</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="72" customHeight="1">
+      <c r="A74" t="inlineStr" s="4">
+        <is>
+          <t>API-005</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="4">
+        <is>
+          <t>Account API</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="4">
+        <is>
+          <t>Lay profile bang Bearer token hop le</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="4">
+        <is>
+          <t>API user moi da duoc tao va co token</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Gui GET /Account/v1/User/{userId}
+2. Gan Authorization Bearer token
+3. Kiem tra thong tin user</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr" s="4">
+        <is>
+          <t>Tra ve 200; userId va username khop; books la mot mang</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr" s="4">
+        <is>
+          <t>userId va token duoc tao dong</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="72" customHeight="1">
+      <c r="A75" t="inlineStr" s="4">
+        <is>
+          <t>API-006</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="4">
+        <is>
+          <t>Account API</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="4">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="4">
+        <is>
+          <t>Tu choi lay profile khi khong co token</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="4">
+        <is>
+          <t>API user moi da duoc tao</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Gui GET /Account/v1/User/{userId}
+2. Khong gui Authorization header
+3. Kiem tra HTTP status</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr" s="4">
+        <is>
+          <t>Tra ve 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr" s="4">
+        <is>
+          <t>userId hop le; khong co token</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api @negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="72" customHeight="1">
+      <c r="A76" t="inlineStr" s="4">
+        <is>
+          <t>API-007</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="4">
+        <is>
+          <t>Book Store API</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="4">
+        <is>
+          <t>Them sach vao collection cua API user</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="4">
+        <is>
+          <t>API user moi da duoc tao va co token; catalog co sach</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Lay sach dau tien trong catalog
+2. Gui POST /BookStore/v1/Books voi userId va isbn
+3. Lay profile de xac minh</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr" s="4">
+        <is>
+          <t>POST tra ve 201; sach da them xuat hien trong books cua profile</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr" s="4">
+        <is>
+          <t>userId, token va isbn duoc tao/lay dong</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="72" customHeight="1">
+      <c r="A77" t="inlineStr" s="4">
+        <is>
+          <t>API-008</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="4">
+        <is>
+          <t>Book Store API</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="4">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="4">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="4">
+        <is>
+          <t>Xoa sach khoi collection cua API user</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="4">
+        <is>
+          <t>API user co mot sach trong collection va co token</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">1. Gui DELETE /BookStore/v1/Book voi isbn va userId
+2. Kiem tra HTTP status
+3. Lay profile de xac minh</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr" s="4">
+        <is>
+          <t>DELETE tra ve 204; collection cua user rong</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr" s="4">
+        <is>
+          <t>userId, token va isbn duoc tao/lay dong</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr" s="4">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr" s="4">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr" s="4">
+        <is>
+          <t>@api @bookstore-api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L69"/>
+  <autoFilter ref="A2:L77"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
